--- a/tests/Day18_Parameterization/testdata/data.xlsx
+++ b/tests/Day18_Parameterization/testdata/data.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\pavan\OneDrive\Desktop\testdata\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://jsainsbury-my.sharepoint.com/personal/joyson_dsouza_sainsburys_co_uk/Documents/Automation/joysonlearning/tests/Day18_Parameterization/testdata/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4CA45082-25B2-4B3B-8413-73A82F09A22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="13_ncr:1_{4CA45082-25B2-4B3B-8413-73A82F09A22F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F793D0F1-2EB4-41CD-A163-EFA785500CFF}"/>
   <bookViews>
-    <workbookView xWindow="16354" yWindow="-103" windowWidth="33120" windowHeight="18000" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20" uniqueCount="17">
   <si>
     <t>email</t>
   </si>
@@ -33,9 +33,6 @@
     <t>password</t>
   </si>
   <si>
-    <t>validity</t>
-  </si>
-  <si>
     <t>laura.taylor1234@example.com</t>
   </si>
   <si>
@@ -61,13 +58,31 @@
   </si>
   <si>
     <t/>
+  </si>
+  <si>
+    <t>attempt</t>
+  </si>
+  <si>
+    <t>attempt_1</t>
+  </si>
+  <si>
+    <t>attempt_2</t>
+  </si>
+  <si>
+    <t>attempt_3</t>
+  </si>
+  <si>
+    <t>attempt_4</t>
+  </si>
+  <si>
+    <t>validation</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -102,6 +117,12 @@
     <font>
       <sz val="16"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -149,7 +170,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
@@ -163,6 +184,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
@@ -444,15 +466,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:C5"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:D5"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="39.54296875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="20.1796875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="9.90625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="45.42578125" customWidth="1"/>
+    <col min="2" max="2" width="20.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="20.140625" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="21" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:4" ht="21" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>0</v>
       </c>
@@ -460,54 +483,70 @@
         <v>1</v>
       </c>
       <c r="C1" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="D1" s="3" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" ht="42" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>2</v>
       </c>
+      <c r="B2" s="2" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>4</v>
+      </c>
+      <c r="D2" s="5" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A2" s="1" t="s">
-        <v>3</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>4</v>
-      </c>
-      <c r="C2" s="2" t="s">
+    <row r="3" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A3" s="1" t="s">
         <v>5</v>
       </c>
+      <c r="B3" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>13</v>
+      </c>
     </row>
-    <row r="3" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
+    <row r="4" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A4" s="1" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C3" s="2" t="s">
-        <v>7</v>
+      <c r="D4" s="5" t="s">
+        <v>14</v>
       </c>
     </row>
-    <row r="4" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A4" s="1" t="s">
-        <v>8</v>
-      </c>
-      <c r="B4" s="2" t="s">
+    <row r="5" spans="1:4" ht="21" x14ac:dyDescent="0.25">
+      <c r="A5" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="5" spans="1:3" ht="21" x14ac:dyDescent="0.35">
-      <c r="A5" s="4" t="s">
-        <v>11</v>
-      </c>
       <c r="B5" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>7</v>
+        <v>6</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>15</v>
       </c>
     </row>
   </sheetData>
+  <phoneticPr fontId="5" type="noConversion"/>
   <hyperlinks>
     <hyperlink ref="A2" r:id="rId1" display="mailto:laura.taylor1234@example.com" xr:uid="{A6ED1AEA-60CA-4F47-9A34-AA4F3749C6C0}"/>
     <hyperlink ref="A3" r:id="rId2" display="mailto:invaliduser@example.com" xr:uid="{73FCDD3D-8DBA-47F2-94DA-D7093FFB5FB4}"/>
